--- a/phase6_evaluation/comparison/evaluation_comparison.xlsx
+++ b/phase6_evaluation/comparison/evaluation_comparison.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluation Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Class Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Threshold Optimization" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,7 +490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eval_005</t>
+          <t>eval_005_exp_005_xgboost_tuned</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -502,34 +504,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9702</v>
+        <v>0.9705</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9391</v>
+        <v>0.9403</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9986</v>
+        <v>0.9987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.969</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9357</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9986</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>10.5092</v>
+        <v>15.11203350014512</v>
       </c>
       <c r="K2" t="n">
-        <v>9063.700000000001</v>
+        <v>66.17243139319386</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eval_001</t>
+          <t>eval_001_exp_001_rf_baseline</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,34 +545,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9597</v>
+        <v>0.9594</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9221</v>
+        <v>0.922</v>
       </c>
       <c r="F3" t="n">
         <v>0.9976</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9607</v>
+        <v>0.961</v>
       </c>
       <c r="H3" t="n">
         <v>0.9234</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9974</v>
+        <v>0.9973</v>
       </c>
       <c r="J3" t="n">
-        <v>24.4103</v>
+        <v>34.86539450000237</v>
       </c>
       <c r="K3" t="n">
-        <v>81137.05</v>
+        <v>28.68173483595409</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>eval_004</t>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -580,38 +582,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ensemble Blending Model</t>
+          <t>Ensemble Blending (RF + GB)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9515</v>
+        <v>0.9534</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9043</v>
+        <v>0.9079</v>
       </c>
       <c r="F4" t="n">
-        <v>0.997</v>
+        <v>0.9971</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9519</v>
+        <v>0.9532</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9043</v>
+        <v>0.9064</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9969</v>
+        <v>0.9967</v>
       </c>
       <c r="J4" t="n">
-        <v>36.4926</v>
+        <v>41.73980049995407</v>
       </c>
       <c r="K4" t="n">
-        <v>21688.79</v>
+        <v>23.95794872093604</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>eval_003</t>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -625,34 +627,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9359</v>
+        <v>0.9357</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8794</v>
+        <v>0.8803</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9913</v>
+        <v>0.9919</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9351</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8793</v>
+        <v>0.8782</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9908</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7701</v>
+        <v>0.1648659999773372</v>
       </c>
       <c r="K5" t="n">
-        <v>5674926.8</v>
+        <v>6065.532008646185</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>eval_002</t>
+          <t>eval_002_exp_002_xgboost_baseline</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -666,28 +668,2495 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>0.9342</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8747</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9953</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9329</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8714</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9.666407499935303</v>
+      </c>
+      <c r="K6" t="n">
+        <v>103.4510494210691</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Eval ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>F1-Score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Random Forest Baseline</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BruteForce</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8148648648648649</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8541076487252125</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8340248962655602</v>
+      </c>
+      <c r="G2" t="n">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Random Forest Baseline</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DDoS</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9994047619047619</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9953561900997925</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9973763675065591</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10121</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Random Forest Baseline</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9990359897172236</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9977535301668806</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9983943481053308</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Random Forest Baseline</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9995805369127517</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.997071129707113</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9983242563887725</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Random Forest Baseline</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7230941704035875</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9097320169252469</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8057464084946908</v>
+      </c>
+      <c r="G6" t="n">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Random Forest Baseline</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9606164383561644</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.893312101910828</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9257425742574258</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Random Forest Baseline</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9334795321637427</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8640054127198917</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8973998594518623</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Random Forest Baseline</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Web-Based</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9096606872703695</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9524779361846571</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9305770506301128</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4419</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gradient Boosting Baseline</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BruteForce</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5707410972088547</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.839943342776204</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6796561604584527</v>
+      </c>
+      <c r="G10" t="n">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gradient Boosting Baseline</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DDoS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9988143464084577</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9994068215521503</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10121</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gradient Boosting Baseline</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9993583573949311</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9996790757381258</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9995186908390823</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gradient Boosting Baseline</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gradient Boosting Baseline</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.6144814090019569</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8857545839210155</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7255921432697863</v>
+      </c>
+      <c r="G14" t="n">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Gradient Boosting Baseline</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9257681776696075</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8075902335456475</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8626506024096385</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gradient Boosting Baseline</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8401122019635343</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8105548037889039</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8250688705234159</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Gradient Boosting Baseline</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Web-Based</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8895066018068103</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8689748811948405</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8791208791208791</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4419</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Decision Tree Baseline</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BruteForce</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.5917753259779338</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8356940509915014</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6928948913681738</v>
+      </c>
+      <c r="G18" t="n">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Decision Tree Baseline</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DDoS</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9989093793376959</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9954549945657544</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9971791953283515</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10121</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Decision Tree Baseline</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9987163029525032</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9993577392421323</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Decision Tree Baseline</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9995814148179154</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.999163179916318</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9993722536095417</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Decision Tree Baseline</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.6267326732673267</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8928067700987306</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7364746945898778</v>
+      </c>
+      <c r="G22" t="n">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Decision Tree Baseline</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.9396578538102643</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8017515923566879</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.8652441643992553</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Decision Tree Baseline</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.8974739970282318</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8173207036535859</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.8555240793201133</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Decision Tree Baseline</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Web-Based</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.8668717047451669</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8929622086444897</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8797235536729462</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4419</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ensemble Blending (RF + GB)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BruteForce</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.6790960451977401</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8512747875354107</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.7554996857322439</v>
+      </c>
+      <c r="G26" t="n">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ensemble Blending (RF + GB)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DDoS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9992095642723051</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9996046258772363</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10121</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ensemble Blending (RF + GB)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9993583573949311</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9996790757381258</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.9995186908390823</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ensemble Blending (RF + GB)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ensemble Blending (RF + GB)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.6914103923647932</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.919605077574048</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.7893462469733656</v>
+      </c>
+      <c r="G30" t="n">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ensemble Blending (RF + GB)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.9526888039964737</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8604033970276008</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9041974619997211</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ensemble Blending (RF + GB)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.9175108538350217</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.857916102841678</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8867132867132868</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ensemble Blending (RF + GB)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Web-Based</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.910818059901654</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9221543335596288</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9164511413471269</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4419</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>XGBoost / Gradient Boosting Tuned</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BruteForce</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.7747524752475248</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.886685552407932</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.8269484808454426</v>
+      </c>
+      <c r="G34" t="n">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>XGBoost / Gradient Boosting Tuned</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DDoS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.9999011857707509</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9998023910680762</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.9998517859789536</v>
+      </c>
+      <c r="G35" t="n">
+        <v>10121</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>XGBoost / Gradient Boosting Tuned</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9993581514762516</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9996789727126806</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>XGBoost / Gradient Boosting Tuned</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>XGBoost / Gradient Boosting Tuned</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.7980416156670747</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.919605077574048</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.854521625163827</v>
+      </c>
+      <c r="G38" t="n">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>XGBoost / Gradient Boosting Tuned</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.9641766176062205</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.921443736730361</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9423259601031347</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>XGBoost / Gradient Boosting Tuned</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.9236016371077762</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9161028416779432</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9198369565217391</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>XGBoost / Gradient Boosting Tuned</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Web-Based</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.9457982236392621</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9398053858338991</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9427922814982974</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4419</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Eval ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Optimal Threshold</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Test Baseline F1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Optimized F1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>F1 Delta (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Optimized Precision</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Optimized Recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BruteForce</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8369</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8733</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8102</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DDoS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9986</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9984</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9987</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8273</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8293</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8196</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8391999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8562</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9225</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9073</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9382</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8712</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9379</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8478</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>eval_001_exp_001_rf_baseline</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Web-Based</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8478</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9273</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9126</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9425</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BruteForce</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7884</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9153</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.704</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DDoS</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9993</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9997</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9996</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8142</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8353</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7941</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.8391</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8617</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8415</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8692</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8051</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>eval_002_exp_002_xgboost_baseline</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Web-Based</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8441</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8912</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8541</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9317</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BruteForce</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7282</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7876</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9254</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6856</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DDoS</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9962</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9987</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9992</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.7754</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8081</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8336</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.7842</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8632</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9529</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.789</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.8598</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8604000000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.7882</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>eval_003_exp_003_decision_tree_baseline</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Web-Based</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.8579</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.8344</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.9455</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BruteForce</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.8312</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8354</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.9043</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.7762</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DDoS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.9993</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8461</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.8761</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8181</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.8586</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9063</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.9144</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.8984</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.8701</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8784999999999999</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.9344</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.8288</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>eval_004_exp_004_ensemble_blending_paper</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Web-Based</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.8624000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9157999999999999</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.8935999999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.9391</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BruteForce</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.8708</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8721</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9067</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.8399</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DDoS</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.9999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.9997</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Mirai</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.8733</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8855</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.9106</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.8618</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recon</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D39" t="n">
         <v>0.9348</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.8749</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.9324</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.8712</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.9951</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7.0118</v>
-      </c>
-      <c r="K6" t="n">
-        <v>24938.92</v>
+      <c r="E39" t="n">
+        <v>0.9432</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.9463</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.9194</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9205</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.9093</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>eval_005_exp_005_xgboost_tuned</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Web-Based</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.9315</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9404</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.9484</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.9326</v>
       </c>
     </row>
   </sheetData>
